--- a/artfynd/A 24411-2023 artfynd.xlsx
+++ b/artfynd/A 24411-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24411-2023 artfynd.xlsx
+++ b/artfynd/A 24411-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100083893</v>
+        <v>100083891</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541404.23958952</v>
+        <v>541471</v>
       </c>
       <c r="R2" t="n">
-        <v>6515621.762690429</v>
+        <v>6515621</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100083891</v>
+        <v>100083893</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541471.2524129963</v>
+        <v>541404</v>
       </c>
       <c r="R3" t="n">
-        <v>6515621.442513936</v>
+        <v>6515622</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2021-11-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-11-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 24411-2023 artfynd.xlsx
+++ b/artfynd/A 24411-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100083891</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100083893</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>